--- a/LongSubmerged10x/Data Sheets/Realistic Travel/General.xlsx
+++ b/LongSubmerged10x/Data Sheets/Realistic Travel/General.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>-8.866666666666667e-08</v>
+        <v>-1.064e-08</v>
       </c>
     </row>
   </sheetData>
